--- a/TemplateExamples/通用模版.xlsx
+++ b/TemplateExamples/通用模版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660" activeTab="2"/>
+    <workbookView windowHeight="15600" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="模板信息" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="375">
   <si>
     <t>模板基本信息（仅第3行有效）</t>
   </si>
@@ -587,12 +587,6 @@
     <t>业务类&gt;code类</t>
   </si>
   <si>
-    <t>序列化对象类</t>
-  </si>
-  <si>
-    <t>业务类&gt;序列化对象类</t>
-  </si>
-  <si>
     <t>标签类</t>
   </si>
   <si>
@@ -767,7 +761,7 @@
     <t>个人年龄信息</t>
   </si>
   <si>
-    <t>(?:[1-9][0-9]?|1[01][0-9]|120)</t>
+    <t>(?:age|年龄|岁数|年岁|岁龄|年龄段|年龄范围|[1-9][0-9]?岁|1[01][0-9]岁|120岁)</t>
   </si>
   <si>
     <t>age</t>
@@ -821,7 +815,7 @@
     <t>个人收入信息</t>
   </si>
   <si>
-    <t>([1-9]\d{0,}|0)(\.\d{1,2})</t>
+    <t>(?:收入|薪资|工资)</t>
   </si>
   <si>
     <t>个人qq号信息</t>
@@ -863,54 +857,117 @@
     <t>公司统一社会信用代码信息</t>
   </si>
   <si>
-    <t>a</t>
+    <t>(?:统一社会信用代码)</t>
   </si>
   <si>
     <t>公司其他信息</t>
   </si>
   <si>
+    <t>(?:公司|企业|集团)</t>
+  </si>
+  <si>
+    <t>(?:公司经营|财务)</t>
+  </si>
+  <si>
     <t>如员工证件信息、任职信息、员工薪酬福利</t>
   </si>
   <si>
+    <t>(?:员工|任职)</t>
+  </si>
+  <si>
     <t>员工薪酬详情信息</t>
   </si>
   <si>
+    <t>(?:薪资|薪酬)</t>
+  </si>
+  <si>
     <t>招投标及采购类表单资料等</t>
   </si>
   <si>
+    <t>(?:招标|投标|招投标)</t>
+  </si>
+  <si>
     <t>公司各合同类信息</t>
   </si>
   <si>
+    <t>(?:合同)</t>
+  </si>
+  <si>
     <t>人事档案类数据</t>
   </si>
   <si>
+    <t>(?:人事档案)</t>
+  </si>
+  <si>
     <t>公司发展规划策略等</t>
   </si>
   <si>
+    <t>(?:发展战略|规划)</t>
+  </si>
+  <si>
     <t>纳税、申报资料</t>
   </si>
   <si>
+    <t>(?:纳税|申报)</t>
+  </si>
+  <si>
     <t>会计凭证数据、账本数据</t>
   </si>
   <si>
+    <t>(?:账本|会计)</t>
+  </si>
+  <si>
     <t>专项等审计数据</t>
   </si>
   <si>
+    <t>(?:专项及经济责任)</t>
+  </si>
+  <si>
+    <t>(?:公司经营)</t>
+  </si>
+  <si>
+    <t>(?:营销方案)</t>
+  </si>
+  <si>
+    <t>(?:产品|运营)</t>
+  </si>
+  <si>
     <t>公司各年度预算数据表单等</t>
   </si>
   <si>
+    <t>(?:年度预算)</t>
+  </si>
+  <si>
+    <t>(?:CP资料|SP资料)</t>
+  </si>
+  <si>
     <t>营销活动表单等信息</t>
   </si>
   <si>
+    <t>(?:营销活动)</t>
+  </si>
+  <si>
     <t>公司规章制度等</t>
   </si>
   <si>
+    <t>(?:制度|规范)</t>
+  </si>
+  <si>
+    <t>(?:法务)</t>
+  </si>
+  <si>
     <t>网络拓扑、IP端口信息等</t>
   </si>
   <si>
+    <t>(?:IT系统|网络)</t>
+  </si>
+  <si>
     <t>研发、测试代码等</t>
   </si>
   <si>
+    <t>(?:研发|代码)</t>
+  </si>
+  <si>
     <t>wechat_app_id,wechat_raw_id,wechat_openid</t>
   </si>
   <si>
@@ -971,7 +1028,7 @@
     <t>设备IDFA信息</t>
   </si>
   <si>
-    <t>([0-9a-zA-Z]{1,})(([/\s-][0-9a-zA-Z]{1,}){4})</t>
+    <t>(?:idfa|IDFA)</t>
   </si>
   <si>
     <t>idfa</t>
@@ -1037,7 +1094,7 @@
     <t>经纬度信息，如"经度116.397128 ，纬度39.916527 "</t>
   </si>
   <si>
-    <t>([\-\+]?(0(\.\d{1,8})?|([1-9](\d)?)(\.\d{1,8})?|1[0-7]\d{1}(\.\d{1,8})?|180(([.][0]{1,8})?)))([\-\+]?((0|([1-8]\d?))(\.\d{1,10})?|90(\.0{1,10})?))</t>
+    <t>(?:latitude|longitude|经纬度)</t>
   </si>
   <si>
     <t>latitude,longitude</t>
@@ -1046,37 +1103,37 @@
     <t>详细收货地址，精确到门牌等</t>
   </si>
   <si>
-    <t>_id</t>
-  </si>
-  <si>
-    <t>_time,time</t>
-  </si>
-  <si>
-    <t>date,_date</t>
-  </si>
-  <si>
-    <t>type,_type</t>
-  </si>
-  <si>
-    <t>status,_status</t>
+    <t>(?:id)</t>
+  </si>
+  <si>
+    <t>(?:time|_time|时间)</t>
+  </si>
+  <si>
+    <t>(?:date|_date|日期)</t>
+  </si>
+  <si>
+    <t>(?:type|_type|类型)</t>
+  </si>
+  <si>
+    <t>(?:status|_status|状态)</t>
   </si>
   <si>
     <t>_name</t>
   </si>
   <si>
-    <t>code,_code</t>
-  </si>
-  <si>
-    <t>tag,_tag</t>
-  </si>
-  <si>
-    <t>num,_num</t>
-  </si>
-  <si>
-    <t>rate,_rate</t>
-  </si>
-  <si>
-    <t>title,_title</t>
+    <t>(?:code|_code|编码|代码)</t>
+  </si>
+  <si>
+    <t>(?:tag|_tag|标签)</t>
+  </si>
+  <si>
+    <t>(?:num|_num|数字|计数)</t>
+  </si>
+  <si>
+    <t>(?:rate|_rate|率)</t>
+  </si>
+  <si>
+    <t>(?:title|_title|标题)</t>
   </si>
   <si>
     <t>数据类型（关联分类、分级、特征）</t>
@@ -1118,7 +1175,7 @@
     <numFmt numFmtId="182" formatCode="0.000000000000000000000000000000000000000000000000"/>
     <numFmt numFmtId="183" formatCode="0.000000000000000000000"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1150,13 +1207,6 @@
       <sz val="12"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1708,28 +1758,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1738,118 +1791,115 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2328,7 +2378,9 @@
   <dimension ref="A1:E200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="26" width="19.9519230769231" customWidth="1"/>
+    <col min="1" max="1" width="19.9519230769231" customWidth="1"/>
+    <col min="2" max="2" width="53.8461538461538" customWidth="1"/>
+    <col min="3" max="26" width="19.9519230769231" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.05" customHeight="1" spans="1:5">
@@ -2584,7 +2636,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z227"/>
+  <dimension ref="A1:Z226"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="28.5576923076923" customWidth="1"/>
@@ -5677,7 +5729,7 @@
         <v>172</v>
       </c>
       <c r="E82" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" s="21"/>
       <c r="G82" s="21"/>
@@ -5715,7 +5767,7 @@
         <v>172</v>
       </c>
       <c r="E83" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F83" s="21"/>
       <c r="G83" s="21"/>
@@ -5753,7 +5805,7 @@
         <v>172</v>
       </c>
       <c r="E84" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F84" s="21"/>
       <c r="G84" s="21"/>
@@ -5791,7 +5843,7 @@
         <v>172</v>
       </c>
       <c r="E85" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F85" s="21"/>
       <c r="G85" s="21"/>
@@ -5816,42 +5868,32 @@
       <c r="Z85" s="21"/>
     </row>
     <row r="86" ht="18.05" customHeight="1" spans="1:26">
-      <c r="A86" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="B86" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D86" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="E86" s="24">
-        <v>12</v>
-      </c>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
-      <c r="I86" s="21"/>
-      <c r="J86" s="21"/>
-      <c r="K86" s="21"/>
-      <c r="L86" s="21"/>
-      <c r="M86" s="21"/>
-      <c r="N86" s="21"/>
-      <c r="O86" s="21"/>
-      <c r="P86" s="21"/>
-      <c r="Q86" s="21"/>
-      <c r="R86" s="21"/>
-      <c r="S86" s="21"/>
-      <c r="T86" s="21"/>
-      <c r="U86" s="21"/>
-      <c r="V86" s="21"/>
-      <c r="W86" s="21"/>
-      <c r="X86" s="21"/>
-      <c r="Y86" s="21"/>
-      <c r="Z86" s="21"/>
+      <c r="A86" s="24"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="20"/>
+      <c r="K86" s="20"/>
+      <c r="L86" s="20"/>
+      <c r="M86" s="20"/>
+      <c r="N86" s="20"/>
+      <c r="O86" s="20"/>
+      <c r="P86" s="20"/>
+      <c r="Q86" s="20"/>
+      <c r="R86" s="20"/>
+      <c r="S86" s="20"/>
+      <c r="T86" s="20"/>
+      <c r="U86" s="20"/>
+      <c r="V86" s="20"/>
+      <c r="W86" s="20"/>
+      <c r="X86" s="20"/>
+      <c r="Y86" s="20"/>
+      <c r="Z86" s="20"/>
     </row>
     <row r="87" ht="18.05" customHeight="1" spans="1:26">
       <c r="A87" s="24"/>
@@ -9773,34 +9815,6 @@
       <c r="Y226" s="20"/>
       <c r="Z226" s="20"/>
     </row>
-    <row r="227" ht="18.05" customHeight="1" spans="1:26">
-      <c r="A227" s="24"/>
-      <c r="B227" s="7"/>
-      <c r="C227" s="7"/>
-      <c r="D227" s="7"/>
-      <c r="E227" s="7"/>
-      <c r="F227" s="20"/>
-      <c r="G227" s="20"/>
-      <c r="H227" s="20"/>
-      <c r="I227" s="20"/>
-      <c r="J227" s="20"/>
-      <c r="K227" s="20"/>
-      <c r="L227" s="20"/>
-      <c r="M227" s="20"/>
-      <c r="N227" s="20"/>
-      <c r="O227" s="20"/>
-      <c r="P227" s="20"/>
-      <c r="Q227" s="20"/>
-      <c r="R227" s="20"/>
-      <c r="S227" s="20"/>
-      <c r="T227" s="20"/>
-      <c r="U227" s="20"/>
-      <c r="V227" s="20"/>
-      <c r="W227" s="20"/>
-      <c r="X227" s="20"/>
-      <c r="Y227" s="20"/>
-      <c r="Z227" s="20"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
@@ -9814,7 +9828,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z200"/>
+  <dimension ref="A1:Z199"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="23.9423076923077" customWidth="1"/>
@@ -9828,7 +9842,7 @@
   <sheetData>
     <row r="1" ht="18.05" customHeight="1" spans="1:26">
       <c r="A1" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -9858,25 +9872,25 @@
     </row>
     <row r="2" ht="19.3" customHeight="1" spans="1:26">
       <c r="A2" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>202</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -9903,22 +9917,22 @@
         <v>17</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -9945,22 +9959,22 @@
         <v>17</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
@@ -9987,22 +10001,22 @@
         <v>21</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G5" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
@@ -10029,22 +10043,22 @@
         <v>21</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -10071,22 +10085,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G7" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -10113,22 +10127,22 @@
         <v>23</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -10155,22 +10169,22 @@
         <v>25</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G9" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -10197,22 +10211,22 @@
         <v>27</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G10" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -10239,22 +10253,22 @@
         <v>29</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G11" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -10281,22 +10295,22 @@
         <v>29</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -10323,22 +10337,22 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G13" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -10365,22 +10379,22 @@
         <v>33</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G14" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -10407,22 +10421,22 @@
         <v>33</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -10449,22 +10463,22 @@
         <v>35</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G16" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -10491,22 +10505,22 @@
         <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G17" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -10533,22 +10547,22 @@
         <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -10575,22 +10589,22 @@
         <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G19" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -10617,22 +10631,22 @@
         <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -10659,22 +10673,22 @@
         <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G21" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -10701,22 +10715,22 @@
         <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -10749,16 +10763,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G23" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -10785,22 +10799,22 @@
         <v>46</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G24" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -10827,22 +10841,22 @@
         <v>46</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -10869,22 +10883,22 @@
         <v>48</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G26" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -10911,22 +10925,22 @@
         <v>48</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -10953,22 +10967,22 @@
         <v>50</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D28" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G28" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -10995,22 +11009,22 @@
         <v>50</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -11037,22 +11051,22 @@
         <v>52</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G30" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -11079,22 +11093,22 @@
         <v>52</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -11121,22 +11135,22 @@
         <v>54</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -11163,22 +11177,22 @@
         <v>56</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D33" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G33" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -11205,22 +11219,22 @@
         <v>58</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D34" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G34" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -11247,22 +11261,22 @@
         <v>60</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G35" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -11289,22 +11303,22 @@
         <v>60</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
@@ -11331,22 +11345,22 @@
         <v>62</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D37" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G37" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
@@ -11373,22 +11387,22 @@
         <v>64</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G38" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
@@ -11415,22 +11429,22 @@
         <v>64</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -11457,22 +11471,22 @@
         <v>66</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D40" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G40" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
@@ -11499,22 +11513,22 @@
         <v>69</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
@@ -11541,22 +11555,22 @@
         <v>71</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G42" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
@@ -11583,22 +11597,22 @@
         <v>74</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D43" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G43" s="10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
@@ -11625,22 +11639,22 @@
         <v>76</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D44" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G44" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
@@ -11667,22 +11681,22 @@
         <v>78</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F45" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G45" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
@@ -11709,19 +11723,19 @@
         <v>80</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D46" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>277</v>
@@ -11751,22 +11765,22 @@
         <v>82</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G47" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
@@ -11799,16 +11813,16 @@
         <v>72</v>
       </c>
       <c r="D48" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G48" s="13" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
@@ -11835,22 +11849,22 @@
         <v>86</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D49" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G49" s="13" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="7"/>
@@ -11877,22 +11891,22 @@
         <v>88</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D50" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G50" s="13" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
@@ -11919,22 +11933,22 @@
         <v>90</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D51" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G51" s="13" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
@@ -11961,22 +11975,22 @@
         <v>92</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D52" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F52" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G52" s="13" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
@@ -12003,22 +12017,22 @@
         <v>94</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D53" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G53" s="13" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
@@ -12045,22 +12059,22 @@
         <v>96</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D54" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G54" s="13" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
@@ -12087,22 +12101,22 @@
         <v>98</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D55" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F55" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G55" s="13" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="7"/>
@@ -12129,22 +12143,22 @@
         <v>100</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D56" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F56" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G56" s="13" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
@@ -12177,16 +12191,16 @@
         <v>72</v>
       </c>
       <c r="D57" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F57" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G57" s="13" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="H57" s="7"/>
       <c r="I57" s="7"/>
@@ -12219,16 +12233,16 @@
         <v>72</v>
       </c>
       <c r="D58" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G58" s="13" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
@@ -12261,16 +12275,16 @@
         <v>72</v>
       </c>
       <c r="D59" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G59" s="13" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="7"/>
@@ -12297,22 +12311,22 @@
         <v>108</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D60" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F60" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G60" s="13" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
@@ -12345,16 +12359,16 @@
         <v>72</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G61" s="13" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
@@ -12381,22 +12395,22 @@
         <v>112</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D62" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G62" s="13" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
@@ -12423,22 +12437,22 @@
         <v>114</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D63" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F63" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G63" s="13" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
@@ -12471,16 +12485,16 @@
         <v>72</v>
       </c>
       <c r="D64" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G64" s="13" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
@@ -12507,22 +12521,22 @@
         <v>118</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G65" s="13" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
@@ -12549,22 +12563,22 @@
         <v>120</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D66" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F66" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G66" s="13" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
@@ -12597,16 +12611,16 @@
         <v>72</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
@@ -12633,22 +12647,22 @@
         <v>124</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D68" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F68" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G68" s="14" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
@@ -12675,22 +12689,22 @@
         <v>127</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D69" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F69" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G69" s="15" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="H69" s="7"/>
       <c r="I69" s="7"/>
@@ -12717,22 +12731,22 @@
         <v>129</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D70" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G70" s="10" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
@@ -12759,20 +12773,20 @@
         <v>129</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="C71" s="16"/>
       <c r="D71" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="H71" s="7"/>
       <c r="I71" s="7"/>
@@ -12799,22 +12813,22 @@
         <v>131</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D72" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F72" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G72" s="10" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
@@ -12841,20 +12855,20 @@
         <v>131</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="C73" s="16"/>
       <c r="D73" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
@@ -12881,22 +12895,22 @@
         <v>133</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D74" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E74" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G74" s="17" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
@@ -12923,22 +12937,22 @@
         <v>135</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D75" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F75" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G75" s="10" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
@@ -12965,22 +12979,22 @@
         <v>137</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D76" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F76" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E76" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G76" s="10" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
@@ -13007,22 +13021,22 @@
         <v>139</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D77" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F77" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G77" s="10" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="H77" s="7"/>
       <c r="I77" s="7"/>
@@ -13049,22 +13063,22 @@
         <v>141</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D78" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F78" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E78" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>313</v>
+      <c r="G78" s="13" t="s">
+        <v>332</v>
       </c>
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
@@ -13091,20 +13105,20 @@
         <v>141</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="C79" s="16"/>
       <c r="D79" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="H79" s="7"/>
       <c r="I79" s="7"/>
@@ -13131,22 +13145,22 @@
         <v>143</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F80" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E80" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G80" s="10" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
@@ -13173,19 +13187,19 @@
         <v>145</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>145</v>
@@ -13221,16 +13235,16 @@
         <v>125</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="H82" s="7"/>
       <c r="I82" s="7"/>
@@ -13257,22 +13271,22 @@
         <v>149</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>150</v>
       </c>
       <c r="D83" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E83" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G83" s="18" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="H83" s="7"/>
       <c r="I83" s="7"/>
@@ -13299,22 +13313,22 @@
         <v>152</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>150</v>
       </c>
       <c r="D84" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F84" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E84" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G84" s="10" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
@@ -13341,20 +13355,20 @@
         <v>152</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="C85" s="16"/>
       <c r="D85" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="H85" s="7"/>
       <c r="I85" s="7"/>
@@ -13385,13 +13399,13 @@
         <v>150</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>154</v>
@@ -13421,22 +13435,22 @@
         <v>156</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>150</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="H87" s="7"/>
       <c r="I87" s="7"/>
@@ -13463,22 +13477,22 @@
         <v>158</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>150</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="H88" s="7"/>
       <c r="I88" s="7"/>
@@ -13505,22 +13519,22 @@
         <v>160</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D89" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G89" s="10" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
@@ -13547,20 +13561,20 @@
         <v>160</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="C90" s="16"/>
       <c r="D90" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
@@ -13587,22 +13601,22 @@
         <v>163</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D91" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E91" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G91" s="10" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
@@ -13629,20 +13643,20 @@
         <v>163</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="C92" s="16"/>
       <c r="D92" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
@@ -13669,22 +13683,22 @@
         <v>165</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D93" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F93" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>335</v>
+      <c r="G93" t="s">
+        <v>354</v>
       </c>
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
@@ -13711,20 +13725,20 @@
         <v>165</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="C94" s="16"/>
       <c r="D94" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
@@ -13751,22 +13765,22 @@
         <v>167</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D95" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F95" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E95" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G95" s="10" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="H95" s="7"/>
       <c r="I95" s="7"/>
@@ -13799,16 +13813,16 @@
         <v>170</v>
       </c>
       <c r="D96" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F96" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E96" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="G96" s="10" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
@@ -13841,16 +13855,16 @@
         <v>170</v>
       </c>
       <c r="D97" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F97" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>339</v>
+      <c r="G97" t="s">
+        <v>358</v>
       </c>
       <c r="H97" s="7"/>
       <c r="I97" s="7"/>
@@ -13883,16 +13897,16 @@
         <v>170</v>
       </c>
       <c r="D98" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F98" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>340</v>
+      <c r="G98" t="s">
+        <v>359</v>
       </c>
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
@@ -13925,16 +13939,16 @@
         <v>170</v>
       </c>
       <c r="D99" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E99" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="G99" s="10" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="H99" s="7"/>
       <c r="I99" s="7"/>
@@ -13967,16 +13981,16 @@
         <v>170</v>
       </c>
       <c r="D100" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F100" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E100" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="G100" s="10" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="H100" s="7"/>
       <c r="I100" s="7"/>
@@ -14009,16 +14023,16 @@
         <v>170</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="H101" s="7"/>
       <c r="I101" s="7"/>
@@ -14051,16 +14065,16 @@
         <v>170</v>
       </c>
       <c r="D102" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F102" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E102" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="G102" s="10" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
@@ -14093,16 +14107,16 @@
         <v>170</v>
       </c>
       <c r="D103" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F103" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E103" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G103" s="13" t="s">
-        <v>277</v>
+      <c r="G103" s="10" t="s">
+        <v>364</v>
       </c>
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
@@ -14135,16 +14149,16 @@
         <v>170</v>
       </c>
       <c r="D104" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F104" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E104" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="G104" s="10" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
@@ -14177,16 +14191,16 @@
         <v>170</v>
       </c>
       <c r="D105" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F105" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E105" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="G105" s="10" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
@@ -14219,16 +14233,16 @@
         <v>170</v>
       </c>
       <c r="D106" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E106" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="G106" s="10" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
@@ -14250,28 +14264,14 @@
       <c r="Y106" s="7"/>
       <c r="Z106" s="7"/>
     </row>
-    <row r="107" ht="19.3" customHeight="1" spans="1:26">
-      <c r="A107" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>348</v>
-      </c>
+    <row r="107" ht="18.05" customHeight="1" spans="1:26">
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="19"/>
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
@@ -16868,34 +16868,6 @@
       <c r="Y199" s="7"/>
       <c r="Z199" s="7"/>
     </row>
-    <row r="200" ht="18.05" customHeight="1" spans="1:26">
-      <c r="A200" s="7"/>
-      <c r="B200" s="7"/>
-      <c r="C200" s="7"/>
-      <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
-      <c r="G200" s="19"/>
-      <c r="H200" s="7"/>
-      <c r="I200" s="7"/>
-      <c r="J200" s="7"/>
-      <c r="K200" s="7"/>
-      <c r="L200" s="7"/>
-      <c r="M200" s="7"/>
-      <c r="N200" s="7"/>
-      <c r="O200" s="7"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="7"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="7"/>
-      <c r="T200" s="7"/>
-      <c r="U200" s="7"/>
-      <c r="V200" s="7"/>
-      <c r="W200" s="7"/>
-      <c r="X200" s="7"/>
-      <c r="Y200" s="7"/>
-      <c r="Z200" s="7"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
@@ -16909,7 +16881,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN200"/>
+  <dimension ref="A1:AN199"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="40" width="19.9519230769231" customWidth="1"/>
@@ -16917,7 +16889,7 @@
   <sheetData>
     <row r="1" ht="18.05" customHeight="1" spans="1:40">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -16961,25 +16933,25 @@
     </row>
     <row r="2" ht="19.3" customHeight="1" spans="1:40">
       <c r="A2" s="3" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -20965,7 +20937,7 @@
       <c r="AM81" s="2"/>
       <c r="AN81" s="2"/>
     </row>
-    <row r="82" ht="29.6" customHeight="1" spans="1:40">
+    <row r="82" ht="19.3" customHeight="1" spans="1:40">
       <c r="A82" s="4" t="s">
         <v>185</v>
       </c>
@@ -21165,22 +21137,14 @@
       <c r="AM85" s="2"/>
       <c r="AN85" s="2"/>
     </row>
-    <row r="86" ht="19.3" customHeight="1" spans="1:40">
-      <c r="A86" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>172</v>
-      </c>
+    <row r="86" ht="18.05" customHeight="1" spans="1:40">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
-      <c r="G86" s="5" t="s">
-        <v>193</v>
-      </c>
+      <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
@@ -25961,48 +25925,6 @@
       <c r="AM199" s="2"/>
       <c r="AN199" s="2"/>
     </row>
-    <row r="200" ht="18.05" customHeight="1" spans="1:40">
-      <c r="A200" s="2"/>
-      <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-      <c r="H200" s="2"/>
-      <c r="I200" s="2"/>
-      <c r="J200" s="2"/>
-      <c r="K200" s="2"/>
-      <c r="L200" s="2"/>
-      <c r="M200" s="2"/>
-      <c r="N200" s="2"/>
-      <c r="O200" s="2"/>
-      <c r="P200" s="2"/>
-      <c r="Q200" s="2"/>
-      <c r="R200" s="2"/>
-      <c r="S200" s="2"/>
-      <c r="T200" s="2"/>
-      <c r="U200" s="2"/>
-      <c r="V200" s="2"/>
-      <c r="W200" s="2"/>
-      <c r="X200" s="2"/>
-      <c r="Y200" s="2"/>
-      <c r="Z200" s="2"/>
-      <c r="AA200" s="2"/>
-      <c r="AB200" s="2"/>
-      <c r="AC200" s="2"/>
-      <c r="AD200" s="2"/>
-      <c r="AE200" s="2"/>
-      <c r="AF200" s="2"/>
-      <c r="AG200" s="2"/>
-      <c r="AH200" s="2"/>
-      <c r="AI200" s="2"/>
-      <c r="AJ200" s="2"/>
-      <c r="AK200" s="2"/>
-      <c r="AL200" s="2"/>
-      <c r="AM200" s="2"/>
-      <c r="AN200" s="2"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
